--- a/artfynd/A 31564-2024 artfynd.xlsx
+++ b/artfynd/A 31564-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4721,6 +4721,233 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122246439</v>
+      </c>
+      <c r="B39" t="n">
+        <v>100388</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>583564</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7055481</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Y-Sol-0431</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122246441</v>
+      </c>
+      <c r="B40" t="n">
+        <v>100388</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>583614</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7055320</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Y-Sol-0430</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31564-2024 artfynd.xlsx
+++ b/artfynd/A 31564-2024 artfynd.xlsx
@@ -4723,10 +4723,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122246439</v>
+        <v>122246441</v>
       </c>
       <c r="B39" t="n">
-        <v>100388</v>
+        <v>100396</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583564</v>
+        <v>583614</v>
       </c>
       <c r="R39" t="n">
-        <v>7055481</v>
+        <v>7055320</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Y-Sol-0431</t>
+          <t>Y-Sol-0430</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4804,6 +4804,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4834,10 +4839,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122246441</v>
+        <v>122246439</v>
       </c>
       <c r="B40" t="n">
-        <v>100388</v>
+        <v>100396</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4874,10 +4879,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583614</v>
+        <v>583564</v>
       </c>
       <c r="R40" t="n">
-        <v>7055320</v>
+        <v>7055481</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4904,7 +4909,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Y-Sol-0430</t>
+          <t>Y-Sol-0431</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4915,11 +4920,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-08-25</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 31564-2024 artfynd.xlsx
+++ b/artfynd/A 31564-2024 artfynd.xlsx
@@ -4723,10 +4723,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122246441</v>
+        <v>122246439</v>
       </c>
       <c r="B39" t="n">
-        <v>100396</v>
+        <v>100398</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583614</v>
+        <v>583564</v>
       </c>
       <c r="R39" t="n">
-        <v>7055320</v>
+        <v>7055481</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Y-Sol-0430</t>
+          <t>Y-Sol-0431</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4804,11 +4804,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-08-25</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4839,10 +4834,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122246439</v>
+        <v>122246441</v>
       </c>
       <c r="B40" t="n">
-        <v>100396</v>
+        <v>100398</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4879,10 +4874,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583564</v>
+        <v>583614</v>
       </c>
       <c r="R40" t="n">
-        <v>7055481</v>
+        <v>7055320</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4909,7 +4904,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Y-Sol-0431</t>
+          <t>Y-Sol-0430</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4920,6 +4915,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 31564-2024 artfynd.xlsx
+++ b/artfynd/A 31564-2024 artfynd.xlsx
@@ -4723,7 +4723,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122246439</v>
+        <v>122246441</v>
       </c>
       <c r="B39" t="n">
         <v>100398</v>
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583564</v>
+        <v>583614</v>
       </c>
       <c r="R39" t="n">
-        <v>7055481</v>
+        <v>7055320</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Y-Sol-0431</t>
+          <t>Y-Sol-0430</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4804,6 +4804,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4834,7 +4839,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122246441</v>
+        <v>122246439</v>
       </c>
       <c r="B40" t="n">
         <v>100398</v>
@@ -4874,10 +4879,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583614</v>
+        <v>583564</v>
       </c>
       <c r="R40" t="n">
-        <v>7055320</v>
+        <v>7055481</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4904,7 +4909,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Y-Sol-0430</t>
+          <t>Y-Sol-0431</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4915,11 +4920,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-08-25</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 31564-2024 artfynd.xlsx
+++ b/artfynd/A 31564-2024 artfynd.xlsx
@@ -4726,7 +4726,7 @@
         <v>122246439</v>
       </c>
       <c r="B39" t="n">
-        <v>100414</v>
+        <v>100424</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>122246441</v>
       </c>
       <c r="B40" t="n">
-        <v>100414</v>
+        <v>100424</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>

--- a/artfynd/A 31564-2024 artfynd.xlsx
+++ b/artfynd/A 31564-2024 artfynd.xlsx
@@ -4723,7 +4723,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122246439</v>
+        <v>122246441</v>
       </c>
       <c r="B39" t="n">
         <v>100424</v>
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583564</v>
+        <v>583614</v>
       </c>
       <c r="R39" t="n">
-        <v>7055481</v>
+        <v>7055320</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Y-Sol-0431</t>
+          <t>Y-Sol-0430</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4804,6 +4804,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4834,7 +4839,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122246441</v>
+        <v>122246439</v>
       </c>
       <c r="B40" t="n">
         <v>100424</v>
@@ -4874,10 +4879,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583614</v>
+        <v>583564</v>
       </c>
       <c r="R40" t="n">
-        <v>7055320</v>
+        <v>7055481</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4904,7 +4909,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Y-Sol-0430</t>
+          <t>Y-Sol-0431</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4915,11 +4920,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-08-25</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 31564-2024 artfynd.xlsx
+++ b/artfynd/A 31564-2024 artfynd.xlsx
@@ -4723,14 +4723,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122246441</v>
+        <v>122246439</v>
       </c>
       <c r="B39" t="n">
-        <v>100424</v>
+        <v>100436</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583614</v>
+        <v>583564</v>
       </c>
       <c r="R39" t="n">
-        <v>7055320</v>
+        <v>7055481</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Y-Sol-0430</t>
+          <t>Y-Sol-0431</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4804,11 +4804,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-08-25</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4839,14 +4834,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122246439</v>
+        <v>122246441</v>
       </c>
       <c r="B40" t="n">
-        <v>100424</v>
+        <v>100436</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4879,10 +4874,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583564</v>
+        <v>583614</v>
       </c>
       <c r="R40" t="n">
-        <v>7055481</v>
+        <v>7055320</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4909,7 +4904,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Y-Sol-0431</t>
+          <t>Y-Sol-0430</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4920,6 +4915,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 31564-2024 artfynd.xlsx
+++ b/artfynd/A 31564-2024 artfynd.xlsx
@@ -4726,7 +4726,7 @@
         <v>122246439</v>
       </c>
       <c r="B39" t="n">
-        <v>100436</v>
+        <v>100441</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>122246441</v>
       </c>
       <c r="B40" t="n">
-        <v>100436</v>
+        <v>100441</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>

--- a/artfynd/A 31564-2024 artfynd.xlsx
+++ b/artfynd/A 31564-2024 artfynd.xlsx
@@ -4726,7 +4726,7 @@
         <v>122246439</v>
       </c>
       <c r="B39" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4740,11 +4740,6 @@
       </c>
       <c r="E39" t="n">
         <v>1365</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Lappranunkel</t>
-        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4837,7 +4832,7 @@
         <v>122246441</v>
       </c>
       <c r="B40" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4851,11 +4846,6 @@
       </c>
       <c r="E40" t="n">
         <v>1365</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Lappranunkel</t>
-        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>

--- a/artfynd/A 31564-2024 artfynd.xlsx
+++ b/artfynd/A 31564-2024 artfynd.xlsx
@@ -4723,10 +4723,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122246439</v>
+        <v>122246441</v>
       </c>
       <c r="B39" t="n">
-        <v>100450</v>
+        <v>100463</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4741,6 +4741,11 @@
       <c r="E39" t="n">
         <v>1365</v>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>Coptidium lapponicum</t>
@@ -4758,10 +4763,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583564</v>
+        <v>583614</v>
       </c>
       <c r="R39" t="n">
-        <v>7055481</v>
+        <v>7055320</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4788,7 +4793,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Y-Sol-0431</t>
+          <t>Y-Sol-0430</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4799,6 +4804,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4829,10 +4839,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122246441</v>
+        <v>122246439</v>
       </c>
       <c r="B40" t="n">
-        <v>100450</v>
+        <v>100463</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4847,6 +4857,11 @@
       <c r="E40" t="n">
         <v>1365</v>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>Coptidium lapponicum</t>
@@ -4864,10 +4879,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583614</v>
+        <v>583564</v>
       </c>
       <c r="R40" t="n">
-        <v>7055320</v>
+        <v>7055481</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4894,7 +4909,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Y-Sol-0430</t>
+          <t>Y-Sol-0431</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4905,11 +4920,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-08-25</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 31564-2024 artfynd.xlsx
+++ b/artfynd/A 31564-2024 artfynd.xlsx
@@ -4723,10 +4723,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122246441</v>
+        <v>122246439</v>
       </c>
       <c r="B39" t="n">
-        <v>100463</v>
+        <v>100476</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583614</v>
+        <v>583564</v>
       </c>
       <c r="R39" t="n">
-        <v>7055320</v>
+        <v>7055481</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Y-Sol-0430</t>
+          <t>Y-Sol-0431</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4804,11 +4804,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-08-25</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4839,10 +4834,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122246439</v>
+        <v>122246441</v>
       </c>
       <c r="B40" t="n">
-        <v>100463</v>
+        <v>100476</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4879,10 +4874,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583564</v>
+        <v>583614</v>
       </c>
       <c r="R40" t="n">
-        <v>7055481</v>
+        <v>7055320</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4909,7 +4904,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Y-Sol-0431</t>
+          <t>Y-Sol-0430</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4920,6 +4915,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 31564-2024 artfynd.xlsx
+++ b/artfynd/A 31564-2024 artfynd.xlsx
@@ -4723,10 +4723,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122246439</v>
+        <v>122246441</v>
       </c>
       <c r="B39" t="n">
-        <v>100476</v>
+        <v>100479</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583564</v>
+        <v>583614</v>
       </c>
       <c r="R39" t="n">
-        <v>7055481</v>
+        <v>7055320</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Y-Sol-0431</t>
+          <t>Y-Sol-0430</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4804,6 +4804,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4834,10 +4839,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122246441</v>
+        <v>122246439</v>
       </c>
       <c r="B40" t="n">
-        <v>100476</v>
+        <v>100479</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4874,10 +4879,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583614</v>
+        <v>583564</v>
       </c>
       <c r="R40" t="n">
-        <v>7055320</v>
+        <v>7055481</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4904,7 +4909,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Y-Sol-0430</t>
+          <t>Y-Sol-0431</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4915,11 +4920,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-08-25</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 31564-2024 artfynd.xlsx
+++ b/artfynd/A 31564-2024 artfynd.xlsx
@@ -4726,7 +4726,7 @@
         <v>122246441</v>
       </c>
       <c r="B39" t="n">
-        <v>100479</v>
+        <v>100480</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>122246439</v>
       </c>
       <c r="B40" t="n">
-        <v>100479</v>
+        <v>100480</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>

--- a/artfynd/A 31564-2024 artfynd.xlsx
+++ b/artfynd/A 31564-2024 artfynd.xlsx
@@ -4726,7 +4726,7 @@
         <v>122246441</v>
       </c>
       <c r="B39" t="n">
-        <v>100480</v>
+        <v>100483</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Y-Sol-0430</t>
+          <t>Y-Sol-0167</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4842,7 +4842,7 @@
         <v>122246439</v>
       </c>
       <c r="B40" t="n">
-        <v>100480</v>
+        <v>100483</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Y-Sol-0431</t>
+          <t>Y-Sol-0168</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">

--- a/artfynd/A 31564-2024 artfynd.xlsx
+++ b/artfynd/A 31564-2024 artfynd.xlsx
@@ -4726,7 +4726,7 @@
         <v>122246441</v>
       </c>
       <c r="B39" t="n">
-        <v>100586</v>
+        <v>100594</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>122246439</v>
       </c>
       <c r="B40" t="n">
-        <v>100586</v>
+        <v>100594</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
